--- a/source/2Bat - Unitats i feina Classroom.xlsx
+++ b/source/2Bat - Unitats i feina Classroom.xlsx
@@ -53,7 +53,7 @@
     <t>30,31,32,21,40,41</t>
   </si>
   <si>
-    <t>46,54,58,92,93,97</t>
+    <t>46,54,58,93,97</t>
   </si>
   <si>
     <t>39, 41, 42, 44, 50, 51, 58</t>
